--- a/260603 New data set (reproducibility)/Overpotnital/Air BP/30K/VC Polyol 1.5bp air_unchanged.xlsx
+++ b/260603 New data set (reproducibility)/Overpotnital/Air BP/30K/VC Polyol 1.5bp air_unchanged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\My Drive\KAIST MASc 2021\Laboratory Work\Protocol\overpotential calculation\For paper SI\260603 New data set (reproducibility)\Overpotnital\Air BP\30K\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D886AB18-3062-4610-A729-6CEFF4F3EF94}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65C9909-B6A5-4DAA-BCD1-4EC80C84FABA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23595" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9503,7 +9503,7 @@
         <v>6.8</v>
       </c>
       <c r="W132">
-        <f t="shared" ref="W132:W163" si="35">V132*$S$5+$S$4</f>
+        <f t="shared" ref="W132:W139" si="35">V132*$S$5+$S$4</f>
         <v>-1.2116639999999999</v>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
     </row>
     <row r="260" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C260">
-        <f t="shared" ref="C260:C323" si="46">A260*B260</f>
+        <f t="shared" ref="C260:C303" si="46">A260*B260</f>
         <v>0</v>
       </c>
       <c r="D260">
@@ -16498,7 +16498,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="e">
-        <f t="shared" ref="P260:P323" si="55">-K260-M260-N260-O260</f>
+        <f t="shared" ref="P260:P303" si="55">-K260-M260-N260-O260</f>
         <v>#NUM!</v>
       </c>
     </row>
@@ -26923,7 +26923,7 @@
         <v>10</v>
       </c>
       <c r="B194">
-        <f t="shared" ref="B194:B257" si="24">A194*200</f>
+        <f t="shared" ref="B194:B223" si="24">A194*200</f>
         <v>2000</v>
       </c>
       <c r="C194">
@@ -26949,14 +26949,14 @@
         <v>0.56898824455633767</v>
       </c>
       <c r="L194">
-        <f t="shared" ref="L194:L257" si="28">K194-$I$1</f>
+        <f t="shared" ref="L194:L223" si="28">K194-$I$1</f>
         <v>-0.65273690721887978</v>
       </c>
       <c r="N194">
         <v>2004.2352000000001</v>
       </c>
       <c r="O194">
-        <f t="shared" ref="O194:O257" si="29">N194/200</f>
+        <f t="shared" ref="O194:O232" si="29">N194/200</f>
         <v>10.021176000000001</v>
       </c>
     </row>
